--- a/submission/knowledge/A08-武汉活动预约官/武汉活动预约官QA导入表.xlsx
+++ b/submission/knowledge/A08-武汉活动预约官/武汉活动预约官QA导入表.xlsx
@@ -384,6 +384,584 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夜游晴川阁免费吗？</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日场须知写免费参观；夜游公开报道为收费演艺。以当天购票页为准。</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晴川夜</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晚上到底看哪个？</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江滩灯光秀免费看江；夜上黄鹤楼进园演艺；游船另票；晴川夜游另票。</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">四件事</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">樱花节要买演出票吗？</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一般不是演出票。樱园可能要景区票；武大要学校预约。</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">花展</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">琴台音乐节在古琴台吗？</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在琴台音乐厅，另一套票。</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">音乐厅</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉街今晚有演唱会？</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">商业活动变化快，看主办方。资料没有就直说。</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">临展</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东湖樱花节要演出票吗？</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一般不是。樱园可能要园中园票。档期看「游东湖」。</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">花展</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">今年渡江节哪天？</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每年不同。看市文旅和主办方。资料没有就直说。</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">渡江</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">琴台音乐节在古琴台景区吗？</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">多在琴台音乐厅，另一套票。</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">音乐节</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东湖夜航等于两江游船吗？</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不是自动同一产品。各看各的售票页。</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夜航</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">活动日地铁还准吗？</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可能管制。问管家，对照官方交通提示。</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">管制</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">灯光秀在游船上才看得到吗？</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不是。大桥至二桥两岸江滩通常可免费看照明。游船是另票产品。</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">灯光秀</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉口江滩和武昌江滩都能看吗？</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">两岸都可见城市景观照明，具体开闭听现场。不是黄鹤楼门票。</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">灯光秀</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">要不要实名预约灯光秀？</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江滩看秀通常不用演出票。若某年有特展购票页，以官方为准。</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">灯光秀</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夜上黄鹤楼和日场联票吗？</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不是自动联票。关注「夜上黄鹤楼」公众号。</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夜场</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夜场能看到编钟乐舞吗？</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">编钟乐舞在省博，须先预约入馆再另购演出票。不是夜上黄鹤楼节目单默认项。</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夜场</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">游船等于1.5元轮渡吗？</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不是。轮渡是公交；夜游船是收费游览产品，航线公开报道多在鹦鹉洲大桥至长江二桥一带。</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">游船</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小孩能上船吗？</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">看购票须知年龄和救生衣要求。我不打包。</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">游船</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夜游晴川阁走哪个号？</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">关注馆方「夜游晴川阁」或「武汉晴川阁大禹文化博物馆」当天入口。日场登记码不能混夜场。</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晴川</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023年68元还适用吗？</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">那是当年报道数字。以当天购票页为准，不写成永久官价。</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晴川</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">编钟乐舞几点开演？</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">须先有入馆预约。场次看馆方公告，资料没有就直说。</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">省博</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东湖菊展要灯光秀票吗？</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不要。花讯看「游东湖」。可能单独售票或延时。</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">花展</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">武大赏樱是活动票吗？</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不是演艺票。学校官方预约，免费限额。</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">武大</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">琴台音乐会在古琴台里面吗？</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">多在琴台音乐厅，另一套票，与景区门票无关。</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">音乐厅</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">春节一定有灯会吗？</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每年不同。看市文旅和主办方。不编「今年必办」。</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">节庆</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东湖马拉松哪天？</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">看主办方报名页。没有知识库条目就直说。</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">节庆</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雨天游船怎么退？</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">按购票须知。我代不了退款。改江滩或回酒店。</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">退改</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">显示没有还能找黄牛吗？</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不能。改免费看江或第二天。</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">余票</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">老人看夜场台阶多吗？</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夜上黄鹤楼仍在蛇山。更稳是江滩平地看照明。</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">家庭</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">散场地铁问谁？</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">交通住宿管家。我把结束时间说清，不报末班钟点。</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">衔接</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黄鹤楼日场几点进？</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">问讲解员。我管夜场和活动档期。</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">帮我锁内部票。</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不能。只给官方入口。</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉街店还开吗？</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">商业开闭问商户助手或导购。我只讲是否有公开演出档期。</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">渡江节要不要买黄鹤楼票？</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">纪念活动与公园门票不是自动一张。各看各的公告。</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">渡江</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">演出日能准时到码头吗？</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可能交通管制。对照官方提示，接驳问管家。</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">管制</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>